--- a/docs/StructureDefinition-mrid-discipline.xlsx
+++ b/docs/StructureDefinition-mrid-discipline.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.8</t>
+    <t>0.5.9</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T11:11:20-06:00</t>
+    <t>2026-02-04T10:26:00-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-mrid-discipline.xlsx
+++ b/docs/StructureDefinition-mrid-discipline.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.12</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T00:24:16-05:00</t>
+    <t>2026-05-25T15:07:02-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-mrid-discipline.xlsx
+++ b/docs/StructureDefinition-mrid-discipline.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:07:02-06:00</t>
+    <t>2026-08-03T22:31:50-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-mrid-discipline.xlsx
+++ b/docs/StructureDefinition-mrid-discipline.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="109">
   <si>
     <t>Property</t>
   </si>
@@ -24,13 +24,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/StructureDefinition/mrid-discipline</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/mrid-discipline</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T22:31:50-05:00</t>
+    <t>2026-09-02T13:24:45-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -88,6 +88,9 @@
   </si>
   <si>
     <t>Copyright</t>
+  </si>
+  <si>
+    <t>Copyright 2022-2026 The MITRE Corporation and Abigail Watson. Licensed under Creative Commons Attribution-NoDerivatives 4.0 International (CC BY-ND 4.0). Approved for Public Release; Distribution Unlimited. Public Release Case Number 25-1124.</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -341,7 +344,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/ValueSet/nasa-mrid-discipline-vs</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/ValueSet/nasa-mrid-discipline-vs</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -590,62 +593,64 @@
       <c r="A14" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -683,7 +688,7 @@
     <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="17.08203125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="55.546875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="70.53515625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
@@ -698,123 +703,123 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -822,10 +827,10 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -837,7 +842,7 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L2" t="s" s="2">
         <v>9</v>
@@ -894,19 +899,19 @@
         <v>20</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK2" t="s" s="2">
         <v>20</v>
@@ -914,10 +919,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -925,10 +930,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -940,13 +945,13 @@
         <v>20</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -997,13 +1002,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -1012,15 +1017,15 @@
         <v>20</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1028,10 +1033,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -1043,13 +1048,13 @@
         <v>20</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1088,31 +1093,31 @@
         <v>20</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AD4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -1120,10 +1125,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1131,10 +1136,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
@@ -1146,16 +1151,16 @@
         <v>20</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1205,13 +1210,13 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
@@ -1220,15 +1225,15 @@
         <v>20</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1236,10 +1241,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -1251,13 +1256,13 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1284,11 +1289,11 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Y6" s="2"/>
       <c r="Z6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -1306,22 +1311,22 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AG6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH6" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ6" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AK6" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="AG6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ6" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK6" t="s" s="2">
-        <v>100</v>
       </c>
     </row>
   </sheetData>
